--- a/data_voor_swing/gebiedsdefinities/kerntypering.xlsx
+++ b/data_voor_swing/gebiedsdefinities/kerntypering.xlsx
@@ -1,68 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\gebiedsniveaus\data_voor_swing\gebiedsdefinities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\gebiedsniveaus\data_voor_swing\gebiedsdefinities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC71049-7632-4977-B302-4554238CAB7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1993AF29-6A3F-448B-B115-D1B6912BD34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4065" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="kerntypering" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
-  <si>
-    <t>volgnr</t>
-  </si>
-  <si>
-    <t>gebiedscode</t>
-  </si>
-  <si>
-    <t>naam_kort</t>
-  </si>
-  <si>
-    <t>naam</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
+  <si>
+    <t>sequence nr</t>
+  </si>
+  <si>
+    <t>geoitem code</t>
+  </si>
+  <si>
+    <t>short name</t>
+  </si>
+  <si>
+    <t>name</t>
   </si>
   <si>
     <t>bovenlokaal</t>
   </si>
   <si>
+    <t>buitende kernen</t>
+  </si>
+  <si>
     <t>lokaal</t>
-  </si>
-  <si>
-    <t>buiten de kernen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -73,12 +69,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -87,7 +98,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -106,9 +119,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -146,7 +159,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -180,7 +193,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -215,10 +227,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -396,62 +407,62 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>